--- a/artfynd/A 30414-2026 artfynd.xlsx
+++ b/artfynd/A 30414-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AZ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109203</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310980</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66481639</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/493099</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/883466</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1503,6 +1543,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66481606</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66481645</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310974</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310977</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310984</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310991</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,6 +2214,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310998</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2251,6 +2326,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311002</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2358,6 +2438,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311006</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,6 +2550,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311010</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2572,6 +2662,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311014</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2679,6 +2774,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311018</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2786,6 +2886,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311023</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2893,6 +2998,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311026</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3000,6 +3110,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311031</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3107,6 +3222,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311042</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3214,6 +3334,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311049</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3321,6 +3446,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311070</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3428,6 +3558,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311072</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3529,6 +3664,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89599626</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3636,6 +3776,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310971</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3743,6 +3888,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310975</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3850,6 +4000,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310979</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3957,6 +4112,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310985</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4064,6 +4224,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310986</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4171,6 +4336,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310993</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4278,6 +4448,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310994</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4385,6 +4560,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310995</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4492,6 +4672,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310999</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4599,6 +4784,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311000</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4706,6 +4896,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311008</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4813,6 +5008,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311013</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4920,6 +5120,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5027,6 +5232,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311029</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5134,6 +5344,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311038</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5241,6 +5456,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311040</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5348,6 +5568,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311045</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5455,6 +5680,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311048</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5562,6 +5792,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311052</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5669,6 +5904,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311057</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5776,6 +6016,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311061</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5883,6 +6128,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311068</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5990,6 +6240,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311071</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6097,6 +6352,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311076</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6204,6 +6464,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311079</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6311,6 +6576,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311081</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6418,6 +6688,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311034</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6525,6 +6800,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311036</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6632,6 +6912,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311073</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6739,6 +7024,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310990</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6846,6 +7136,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311033</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6953,6 +7248,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311065</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7060,6 +7360,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311066</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7167,6 +7472,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311067</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7274,6 +7584,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311016</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7381,6 +7696,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311043</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7482,6 +7802,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89599635</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7589,6 +7914,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310973</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7696,6 +8026,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310976</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7803,6 +8138,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310992</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7910,6 +8250,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310997</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8017,6 +8362,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311001</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8124,6 +8474,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311005</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8231,6 +8586,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311009</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8338,6 +8698,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311017</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8445,6 +8810,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311030</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8552,6 +8922,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311044</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8659,6 +9034,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311050</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8766,6 +9146,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311028</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8863,6 +9248,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2023288</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8970,6 +9360,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311041</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9082,6 +9477,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311086</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9194,6 +9594,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310978</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9306,6 +9711,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311003</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9418,6 +9828,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311056</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9530,6 +9945,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311087</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9637,6 +10057,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311063</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9758,6 +10183,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310987</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9874,6 +10304,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311004</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9981,6 +10416,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311007</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10088,6 +10528,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311015</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10204,6 +10649,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311021</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10325,6 +10775,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311022</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10446,6 +10901,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311062</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10562,6 +11022,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311074</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10669,6 +11134,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311075</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10785,6 +11255,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311077</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10901,6 +11376,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311078</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11022,6 +11502,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311083</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11138,6 +11623,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311085</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11245,6 +11735,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310996</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11352,6 +11847,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311011</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11459,6 +11959,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311020</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11566,6 +12071,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311024</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11673,6 +12183,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311046</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11780,6 +12295,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311064</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11887,6 +12407,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311069</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11994,6 +12519,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311082</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12101,6 +12631,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310983</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12208,6 +12743,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310989</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12315,6 +12855,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311032</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12422,6 +12967,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311035</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12529,6 +13079,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311037</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12636,6 +13191,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311054</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12743,6 +13303,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310972</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12850,6 +13415,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311027</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12957,6 +13527,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135310988</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13064,8 +13639,130 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311055</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30414-2026 artfynd.xlsx
+++ b/artfynd/A 30414-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135310980</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135311019</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>135310974</v>
       </c>
       <c r="B11" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>135310977</v>
       </c>
       <c r="B12" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>135310984</v>
       </c>
       <c r="B13" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>135310991</v>
       </c>
       <c r="B14" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>135310998</v>
       </c>
       <c r="B15" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135311002</v>
       </c>
       <c r="B16" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>135311006</v>
       </c>
       <c r="B17" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>135311010</v>
       </c>
       <c r="B18" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>135311014</v>
       </c>
       <c r="B19" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>135311018</v>
       </c>
       <c r="B20" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>135311023</v>
       </c>
       <c r="B21" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135311026</v>
       </c>
       <c r="B22" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>135311031</v>
       </c>
       <c r="B23" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>135311042</v>
       </c>
       <c r="B24" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>135311049</v>
       </c>
       <c r="B25" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>135311070</v>
       </c>
       <c r="B26" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>135311072</v>
       </c>
       <c r="B27" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>135310971</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>135310975</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>135310979</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135310985</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>135310986</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>135310993</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>135310994</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>135310995</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135310999</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>135311000</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>135311008</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>135311013</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>135311025</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>135311029</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>135311038</v>
       </c>
       <c r="B43" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>135311040</v>
       </c>
       <c r="B44" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>135311045</v>
       </c>
       <c r="B45" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>135311048</v>
       </c>
       <c r="B46" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>135311052</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>135311057</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>135311061</v>
       </c>
       <c r="B49" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>135311068</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>135311071</v>
       </c>
       <c r="B51" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>135311076</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>135311079</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>135311081</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>135311034</v>
       </c>
       <c r="B55" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>135311036</v>
       </c>
       <c r="B56" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>135311073</v>
       </c>
       <c r="B57" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>135310990</v>
       </c>
       <c r="B58" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>135311033</v>
       </c>
       <c r="B59" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>135311065</v>
       </c>
       <c r="B60" t="n">
-        <v>80413</v>
+        <v>80451</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>135311066</v>
       </c>
       <c r="B61" t="n">
-        <v>80413</v>
+        <v>80451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>135311067</v>
       </c>
       <c r="B62" t="n">
-        <v>80413</v>
+        <v>80451</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>135311016</v>
       </c>
       <c r="B63" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>135311043</v>
       </c>
       <c r="B64" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>135310973</v>
       </c>
       <c r="B66" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>135310976</v>
       </c>
       <c r="B67" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>135310992</v>
       </c>
       <c r="B68" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>135310997</v>
       </c>
       <c r="B69" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>135311001</v>
       </c>
       <c r="B70" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>135311005</v>
       </c>
       <c r="B71" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>135311009</v>
       </c>
       <c r="B72" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>135311017</v>
       </c>
       <c r="B73" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>135311030</v>
       </c>
       <c r="B74" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>135311044</v>
       </c>
       <c r="B75" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>135311050</v>
       </c>
       <c r="B76" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>135311028</v>
       </c>
       <c r="B77" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>135311041</v>
       </c>
       <c r="B79" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>135311086</v>
       </c>
       <c r="B80" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>135310978</v>
       </c>
       <c r="B81" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>135311003</v>
       </c>
       <c r="B82" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>135311056</v>
       </c>
       <c r="B83" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>135311087</v>
       </c>
       <c r="B84" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>135311063</v>
       </c>
       <c r="B85" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>135310987</v>
       </c>
       <c r="B86" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>135311004</v>
       </c>
       <c r="B87" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>135311007</v>
       </c>
       <c r="B88" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>135311015</v>
       </c>
       <c r="B89" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>135311021</v>
       </c>
       <c r="B90" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>135311022</v>
       </c>
       <c r="B91" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>135311062</v>
       </c>
       <c r="B92" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>135311074</v>
       </c>
       <c r="B93" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>135311075</v>
       </c>
       <c r="B94" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>135311077</v>
       </c>
       <c r="B95" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>135311078</v>
       </c>
       <c r="B96" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>135311083</v>
       </c>
       <c r="B97" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>135311085</v>
       </c>
       <c r="B98" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>135310996</v>
       </c>
       <c r="B99" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>135311011</v>
       </c>
       <c r="B100" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135311020</v>
       </c>
       <c r="B101" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>135311024</v>
       </c>
       <c r="B102" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>135311046</v>
       </c>
       <c r="B103" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>135311064</v>
       </c>
       <c r="B104" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>135311069</v>
       </c>
       <c r="B105" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>135311082</v>
       </c>
       <c r="B106" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>135310983</v>
       </c>
       <c r="B107" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>135310989</v>
       </c>
       <c r="B108" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>135311032</v>
       </c>
       <c r="B109" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>135311035</v>
       </c>
       <c r="B110" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>135311037</v>
       </c>
       <c r="B111" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>135311054</v>
       </c>
       <c r="B112" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>135310972</v>
       </c>
       <c r="B113" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>135311027</v>
       </c>
       <c r="B114" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>135310988</v>
       </c>
       <c r="B115" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>135311055</v>
       </c>
       <c r="B116" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 30414-2026 artfynd.xlsx
+++ b/artfynd/A 30414-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135310980</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135311019</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>135310974</v>
       </c>
       <c r="B11" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>135310977</v>
       </c>
       <c r="B12" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>135310984</v>
       </c>
       <c r="B13" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>135310991</v>
       </c>
       <c r="B14" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>135310998</v>
       </c>
       <c r="B15" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135311002</v>
       </c>
       <c r="B16" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>135311006</v>
       </c>
       <c r="B17" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>135311010</v>
       </c>
       <c r="B18" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>135311014</v>
       </c>
       <c r="B19" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>135311018</v>
       </c>
       <c r="B20" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>135311023</v>
       </c>
       <c r="B21" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135311026</v>
       </c>
       <c r="B22" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>135311031</v>
       </c>
       <c r="B23" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>135311042</v>
       </c>
       <c r="B24" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>135311049</v>
       </c>
       <c r="B25" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>135311070</v>
       </c>
       <c r="B26" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>135311072</v>
       </c>
       <c r="B27" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>135310971</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>135310975</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>135310979</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135310985</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>135310986</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>135310993</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>135310994</v>
       </c>
       <c r="B35" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>135310995</v>
       </c>
       <c r="B36" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135310999</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>135311000</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>135311008</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>135311013</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>135311025</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>135311029</v>
       </c>
       <c r="B42" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>135311038</v>
       </c>
       <c r="B43" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>135311040</v>
       </c>
       <c r="B44" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>135311045</v>
       </c>
       <c r="B45" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>135311048</v>
       </c>
       <c r="B46" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>135311052</v>
       </c>
       <c r="B47" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>135311057</v>
       </c>
       <c r="B48" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>135311061</v>
       </c>
       <c r="B49" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>135311068</v>
       </c>
       <c r="B50" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>135311071</v>
       </c>
       <c r="B51" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>135311076</v>
       </c>
       <c r="B52" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>135311079</v>
       </c>
       <c r="B53" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>135311081</v>
       </c>
       <c r="B54" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>135311034</v>
       </c>
       <c r="B55" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>135311036</v>
       </c>
       <c r="B56" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>135311073</v>
       </c>
       <c r="B57" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>135310990</v>
       </c>
       <c r="B58" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>135311033</v>
       </c>
       <c r="B59" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>135311065</v>
       </c>
       <c r="B60" t="n">
-        <v>80451</v>
+        <v>80478</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>135311066</v>
       </c>
       <c r="B61" t="n">
-        <v>80451</v>
+        <v>80478</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>135311067</v>
       </c>
       <c r="B62" t="n">
-        <v>80451</v>
+        <v>80478</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>135311016</v>
       </c>
       <c r="B63" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>135311043</v>
       </c>
       <c r="B64" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>135310973</v>
       </c>
       <c r="B66" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>135310976</v>
       </c>
       <c r="B67" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>135310992</v>
       </c>
       <c r="B68" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>135310997</v>
       </c>
       <c r="B69" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>135311001</v>
       </c>
       <c r="B70" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>135311005</v>
       </c>
       <c r="B71" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>135311009</v>
       </c>
       <c r="B72" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>135311017</v>
       </c>
       <c r="B73" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>135311030</v>
       </c>
       <c r="B74" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>135311044</v>
       </c>
       <c r="B75" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>135311050</v>
       </c>
       <c r="B76" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>135311028</v>
       </c>
       <c r="B77" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>135311041</v>
       </c>
       <c r="B79" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>135311063</v>
       </c>
       <c r="B85" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>135310987</v>
       </c>
       <c r="B86" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>135311004</v>
       </c>
       <c r="B87" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>135311007</v>
       </c>
       <c r="B88" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>135311015</v>
       </c>
       <c r="B89" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>135311021</v>
       </c>
       <c r="B90" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>135311022</v>
       </c>
       <c r="B91" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>135311062</v>
       </c>
       <c r="B92" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>135311074</v>
       </c>
       <c r="B93" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>135311075</v>
       </c>
       <c r="B94" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>135311077</v>
       </c>
       <c r="B95" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>135311078</v>
       </c>
       <c r="B96" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>135311083</v>
       </c>
       <c r="B97" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>135311085</v>
       </c>
       <c r="B98" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>135310996</v>
       </c>
       <c r="B99" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>135311011</v>
       </c>
       <c r="B100" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135311020</v>
       </c>
       <c r="B101" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>135311024</v>
       </c>
       <c r="B102" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>135311046</v>
       </c>
       <c r="B103" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>135311064</v>
       </c>
       <c r="B104" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>135311069</v>
       </c>
       <c r="B105" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>135311082</v>
       </c>
       <c r="B106" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>135310983</v>
       </c>
       <c r="B107" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>135310989</v>
       </c>
       <c r="B108" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>135311032</v>
       </c>
       <c r="B109" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>135311035</v>
       </c>
       <c r="B110" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>135311037</v>
       </c>
       <c r="B111" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>135311054</v>
       </c>
       <c r="B112" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>135310972</v>
       </c>
       <c r="B113" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>135311027</v>
       </c>
       <c r="B114" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>135310988</v>
       </c>
       <c r="B115" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>135311055</v>
       </c>
       <c r="B116" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 30414-2026 artfynd.xlsx
+++ b/artfynd/A 30414-2026 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>135311019</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>135311063</v>
       </c>
       <c r="B85" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>135310987</v>
       </c>
       <c r="B86" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>135311004</v>
       </c>
       <c r="B87" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>135311007</v>
       </c>
       <c r="B88" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>135311015</v>
       </c>
       <c r="B89" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>135311021</v>
       </c>
       <c r="B90" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>135311022</v>
       </c>
       <c r="B91" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>135311062</v>
       </c>
       <c r="B92" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>135311074</v>
       </c>
       <c r="B93" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>135311075</v>
       </c>
       <c r="B94" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>135311077</v>
       </c>
       <c r="B95" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>135311078</v>
       </c>
       <c r="B96" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>135311083</v>
       </c>
       <c r="B97" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>135311085</v>
       </c>
       <c r="B98" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>135310996</v>
       </c>
       <c r="B99" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>135311011</v>
       </c>
       <c r="B100" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135311020</v>
       </c>
       <c r="B101" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>135311024</v>
       </c>
       <c r="B102" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>135311046</v>
       </c>
       <c r="B103" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>135311064</v>
       </c>
       <c r="B104" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>135311069</v>
       </c>
       <c r="B105" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>135311082</v>
       </c>
       <c r="B106" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
